--- a/maze_trajectory_gt_confusion.xlsx
+++ b/maze_trajectory_gt_confusion.xlsx
@@ -625,7 +625,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
         <is>
           <t>TP=4 FP=0
 FN=2 TN=0
-SW=2</t>
+SW=1</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -915,7 +915,7 @@
         <is>
           <t>TP=0 FP=0
 FN=3 TN=0
-SW=3</t>
+SW=1</t>
         </is>
       </c>
     </row>
@@ -932,14 +932,14 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
           <t>TP=2 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>TP=5 FP=0
-FN=1 TN=0</t>
+FN=4 TN=0</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -947,10 +947,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>TP=6 FP=0
-FN=0 TN=0</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=2 TN=0</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -981,8 +981,8 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>TP=2 FP=0
-FN=1 TN=0</t>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
         </is>
       </c>
     </row>
@@ -999,339 +999,339 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>TP=0 FP=1
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=3</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=3 TN=2</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>at(p,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=4 TN=0
+SW=3</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>TP=4 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0
+SW=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>clear(to)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t>TP=1 FP=0
 FN=2 TN=0</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>TP=4 FP=0
 FN=2 TN=0</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TP=3 FP=0
 FN=3 TN=0</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
+FN=2 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>oriented-down(p)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=6</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=5</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>DEL</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>at(p,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>oriented-left(p)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=5
-SW=1</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=1
+FN=1 TN=3</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=6
-SW=0</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>clear(to)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
+FN=1 TN=5</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>oriented-down(p)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=3</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=6</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>oriented-left(p)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=5</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=6</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1346,14 +1346,14 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
+          <t>TP=0 FP=1
+FN=1 TN=1</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TP=0 FP=1
-FN=0 TN=5</t>
+          <t>TP=0 FP=0
+FN=1 TN=5</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1363,40 +1363,40 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
+          <t>TP=2 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
           <t>TP=0 FP=0
-FN=0 TN=6</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
+FN=1 TN=2</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -1781,7 +1781,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
         <is>
           <t>TP=1 FP=0
 FN=3 TN=0
-SW=3</t>
+SW=2</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1829,7 +1829,7 @@
         <is>
           <t>TP=1 FP=0
 FN=1 TN=0
-SW=1</t>
+SW=0</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -1843,512 +1843,512 @@
         <is>
           <t>TP=1 FP=0
 FN=3 TN=0
-SW=3</t>
+SW=2</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=4 TN=0
-SW=4</t>
+SW=3</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0
+SW=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>clear(from)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>oriented-down(p)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=2</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=1</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>at(p,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=2 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=1 TN=0
 SW=1</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>clear(from)</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0
+SW=3</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=3 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0
+SW=3</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0
+SW=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>clear(to)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=3 TN=0</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>oriented-up(p)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>oriented-left(p)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=3</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>oriented-right(p)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=4 TN=0</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>oriented-down(p)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=4 TN=0</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>at(p,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2
-SW=2</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1
-SW=1</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2
-SW=2</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2
-SW=2</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=0
-SW=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>clear(to)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>oriented-up(p)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>oriented-left(p)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=4</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
 FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>oriented-right(p)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -2511,7 +2511,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -2751,8 +2751,8 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>TP=1 FP=0
-FN=1 TN=0
+          <t>TP=0 FP=0
+FN=2 TN=0
 SW=1</t>
         </is>
       </c>
@@ -2767,7 +2767,7 @@
         <is>
           <t>TP=1 FP=0
 FN=2 TN=0
-SW=2</t>
+SW=0</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -2823,460 +2823,460 @@
           <t>clear(from)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>TP=2 FP=0
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>oriented-left(p)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>at(p,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=0 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=1 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>clear(to)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=0</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>TP=2 FP=0
 FN=0 TN=0</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>TP=2 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>oriented-down(p)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>oriented-up(p)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>oriented-left(p)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>oriented-right(p)</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>at(p,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
-SW=0</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
-SW=0</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2
-SW=1</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1
-SW=0</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2
-SW=0</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>clear(to)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>oriented-down(p)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>oriented-up(p)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>oriented-right(p)</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1</t>
+FN=1 TN=0</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -3454,7 +3454,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>PRECONDITIONS (in prev state)</t>
+          <t>PRECONDITIONS (present in prev state)</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADD EFFECTS (in next state)</t>
+          <t>ADD EFFECTS (absent in prev → present in next)</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
         <is>
           <t>TP=0 FP=0
 FN=1 TN=0
-SW=1</t>
+SW=0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3732,560 +3732,560 @@
         <is>
           <t>TP=1 FP=0
 FN=3 TN=0
-SW=3</t>
+SW=1</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=2 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=3 TN=0
 SW=2</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=2 TN=0
+SW=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>clear(from)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>oriented-right(p)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>TP=3 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=1</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=1
+FN=1 TN=1</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>DELETE EFFECTS (present in prev → absent in next)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>at(p,from)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=0
+SW=0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=1 TN=0
 SW=1</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
 FN=2 TN=0
 SW=2</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0
+SW=2</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=3 TN=0
+SW=1</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=4 TN=0
+SW=3</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
 FN=3 TN=0
-SW=3</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=2 TN=0
 SW=2</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>clear(from)</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>clear(to)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=0</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=1 TN=0</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=3 TN=0</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>TP=2 FP=0
+FN=1 TN=0</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=3 TN=0</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
 FN=2 TN=0</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=1 TN=0</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>TP=3 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>oriented-right(p)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>TP=1 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>oriented-down(p)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
 FN=2 TN=0</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>TP=4 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=2
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
+FN=1 TN=1</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=3 TN=0</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>TP=2 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>TP=1 FP=0
-FN=2 TN=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>DELETE EFFECTS (absent from next state)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+FN=1 TN=2</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=1 TN=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>DEL</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>at(p,from)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>oriented-left(p)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
-FN=0 TN=0
-SW=1</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=2
-SW=0</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
+FN=0 TN=4</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=1
+FN=0 TN=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>oriented-up(p)</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=2
-SW=0</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=1
-SW=3</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1
-SW=2</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=1
-SW=1</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1
-SW=2</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2
-SW=2</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
+FN=0 TN=1</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=0
-FN=0 TN=3
-SW=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>clear(to)</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+FN=1 TN=1</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>TP=0 FP=0
+FN=2 TN=2</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
 FN=0 TN=2</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
 FN=0 TN=1</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>TP=1 FP=0
+FN=0 TN=2</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
+FN=0 TN=3</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>TP=1 FP=1
 FN=0 TN=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>oriented-down(p)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>oriented-left(p)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=3
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>oriented-up(p)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=0</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=4</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=3</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>TP=0 FP=0
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=1</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=2
-FN=0 TN=2</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>TP=0 FP=1
-FN=0 TN=2</t>
         </is>
       </c>
     </row>
